--- a/Early cancer detection/TS Train.xlsx
+++ b/Early cancer detection/TS Train.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30106"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\01_PhD\BaiduSyncdisk\PhD\09_文章数据\TS Prediction_RF_LDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSoft\Pycharm\PythonProject\PythonProject\Archive\01_tri_cancer_screening\Source code for submission\Early cancer detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9746B2-27A7-44B7-A6B8-167667DE37FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B06914B-BF4C-423A-A193-9CE9487A09E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="1200" windowWidth="16236" windowHeight="14604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="7" r:id="rId1"/>
-    <sheet name="Source" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,127 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="68">
-  <si>
-    <t>(6,4)-N20__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N19__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N18__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N17__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N15__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N14__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N12__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N11__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X25__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X30__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X29__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X28__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X27__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X26__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N10__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N9__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N8__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N7__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N6__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N5__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N4__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N3__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N2__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N1__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N10n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N9n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N8n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N7n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N6n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N5n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N4n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N3n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N2n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-N1n__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X10__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X9__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X8__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X7__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X5__660</t>
-  </si>
-  <si>
-    <t>(6,4)-X3__660</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="15">
   <si>
     <t>dint(6,4)</t>
   </si>
@@ -175,9 +54,6 @@
   </si>
   <si>
     <t>dint(9,1)</t>
-  </si>
-  <si>
-    <t>Sample ID</t>
   </si>
   <si>
     <t>Sample</t>
@@ -210,45 +86,7 @@
     <t>LuC</t>
   </si>
   <si>
-    <t>(6,4)-X32__660</t>
-  </si>
-  <si>
     <t>N</t>
-  </si>
-  <si>
-    <t>X10</t>
-  </si>
-  <si>
-    <t>X9</t>
-  </si>
-  <si>
-    <t>(6,4)-X33__660</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(6,4)-X34__660</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>X11</t>
-  </si>
-  <si>
-    <t>X7</t>
-  </si>
-  <si>
-    <t>X6</t>
-  </si>
-  <si>
-    <t>X5</t>
-  </si>
-  <si>
-    <t>X4</t>
-  </si>
-  <si>
-    <t>X3</t>
-  </si>
-  <si>
-    <t>X2</t>
   </si>
 </sst>
 </file>
@@ -258,7 +96,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -391,14 +229,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -417,13 +247,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -709,59 +533,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4D32A6-BAC1-4CF0-87E7-2BD375B36B4D}">
   <dimension ref="A1:O64"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="1" customWidth="1"/>
     <col min="2" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="8.88671875" style="30"/>
+    <col min="7" max="7" width="8.88671875" style="24"/>
     <col min="8" max="13" width="8.88671875" style="1"/>
     <col min="14" max="14" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>40</v>
+        <v>1</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>0</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B2" s="7">
         <v>-1.04538</v>
@@ -778,10 +602,10 @@
       <c r="F2" s="7">
         <v>0.83172000000000001</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="18">
         <v>0.29249999999999998</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="7">
         <v>-0.61443000000000003</v>
       </c>
       <c r="I2" s="7">
@@ -802,9 +626,9 @@
       <c r="N2" s="6"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B3" s="7">
         <v>-0.70243</v>
@@ -821,10 +645,10 @@
       <c r="F3" s="7">
         <v>0.54937999999999998</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="18">
         <v>0.58689000000000002</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="7">
         <v>-0.40277000000000002</v>
       </c>
       <c r="I3" s="7">
@@ -845,9 +669,9 @@
       <c r="N3" s="6"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B4" s="7">
         <v>-1.30525</v>
@@ -864,10 +688,10 @@
       <c r="F4" s="7">
         <v>0.22789000000000001</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="18">
         <v>-3.397E-2</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="7">
         <v>-0.67196999999999996</v>
       </c>
       <c r="I4" s="7">
@@ -888,9 +712,9 @@
       <c r="N4" s="6"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B5" s="7">
         <v>-0.63944999999999996</v>
@@ -907,10 +731,10 @@
       <c r="F5" s="7">
         <v>0.26618000000000003</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="18">
         <v>0.67571000000000003</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="7">
         <v>-0.52639999999999998</v>
       </c>
       <c r="I5" s="7">
@@ -931,9 +755,9 @@
       <c r="N5" s="6"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B6" s="7">
         <v>-1.1816199999999999</v>
@@ -950,10 +774,10 @@
       <c r="F6" s="7">
         <v>-0.63887000000000005</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="18">
         <v>-0.20804</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="7">
         <v>-1.5779999999999999E-2</v>
       </c>
       <c r="I6" s="7">
@@ -974,9 +798,9 @@
       <c r="N6" s="6"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B7" s="7">
         <v>-0.87936000000000003</v>
@@ -993,10 +817,10 @@
       <c r="F7" s="7">
         <v>0.20882999999999999</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="18">
         <v>0.58726999999999996</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="7">
         <v>-0.49909999999999999</v>
       </c>
       <c r="I7" s="7">
@@ -1017,9 +841,9 @@
       <c r="N7" s="6"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B8" s="13">
         <v>0.35000999999999999</v>
@@ -1036,10 +860,10 @@
       <c r="F8" s="13">
         <v>2.5870000000000001E-2</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="19">
         <v>0.24604999999999999</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="13">
         <v>-0.89485999999999999</v>
       </c>
       <c r="I8" s="13">
@@ -1060,9 +884,9 @@
       <c r="N8" s="12"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B9" s="13">
         <v>-1.1359300000000001</v>
@@ -1079,10 +903,10 @@
       <c r="F9" s="13">
         <v>0.66785000000000005</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="19">
         <v>0.82333000000000001</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="13">
         <v>-1.10778</v>
       </c>
       <c r="I9" s="13">
@@ -1103,9 +927,9 @@
       <c r="N9" s="12"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B10" s="13">
         <v>-1.13063</v>
@@ -1122,10 +946,10 @@
       <c r="F10" s="13">
         <v>0.59038000000000002</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="19">
         <v>0.58965999999999996</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="13">
         <v>-1.33385</v>
       </c>
       <c r="I10" s="13">
@@ -1146,9 +970,9 @@
       <c r="N10" s="12"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B11" s="13">
         <v>-1.4419</v>
@@ -1165,10 +989,10 @@
       <c r="F11" s="13">
         <v>-1.31118</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="19">
         <v>-1.04915</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="13">
         <v>-0.25669999999999998</v>
       </c>
       <c r="I11" s="13">
@@ -1189,9 +1013,9 @@
       <c r="N11" s="12"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B12" s="13">
         <v>-1.4561299999999999</v>
@@ -1208,10 +1032,10 @@
       <c r="F12" s="13">
         <v>0.56967999999999996</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="19">
         <v>0.34127000000000002</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="13">
         <v>-1.3644400000000001</v>
       </c>
       <c r="I12" s="13">
@@ -1232,9 +1056,9 @@
       <c r="N12" s="12"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B13" s="13">
         <v>2.1588599999999998</v>
@@ -1251,10 +1075,10 @@
       <c r="F13" s="13">
         <v>-5.2220000000000003E-2</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="19">
         <v>-0.40466000000000002</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="13">
         <v>-0.48393000000000003</v>
       </c>
       <c r="I13" s="13">
@@ -1275,9 +1099,9 @@
       <c r="N13" s="12"/>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B14" s="13">
         <v>1.2878499999999999</v>
@@ -1294,10 +1118,10 @@
       <c r="F14" s="13">
         <v>0.25631999999999999</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="19">
         <v>8.6800000000000002E-2</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="13">
         <v>-0.58352999999999999</v>
       </c>
       <c r="I14" s="13">
@@ -1318,9 +1142,9 @@
       <c r="N14" s="12"/>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B15" s="13">
         <v>-0.56979999999999997</v>
@@ -1337,10 +1161,10 @@
       <c r="F15" s="13">
         <v>0.33300999999999997</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="19">
         <v>-0.21743999999999999</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="13">
         <v>-0.67100000000000004</v>
       </c>
       <c r="I15" s="13">
@@ -1361,9 +1185,9 @@
       <c r="N15" s="12"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B16" s="13">
         <v>-1.2387900000000001</v>
@@ -1380,10 +1204,10 @@
       <c r="F16" s="13">
         <v>0.21582999999999999</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="19">
         <v>-0.40648000000000001</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="13">
         <v>-1.4386699999999999</v>
       </c>
       <c r="I16" s="13">
@@ -1404,9 +1228,9 @@
       <c r="N16" s="12"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B17" s="10">
         <v>-0.87280999999999997</v>
@@ -1423,10 +1247,10 @@
       <c r="F17" s="10">
         <v>0.65042999999999995</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="20">
         <v>0.70631999999999995</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="10">
         <v>-1.1612</v>
       </c>
       <c r="I17" s="10">
@@ -1447,9 +1271,9 @@
       <c r="N17" s="6"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B18" s="10">
         <v>-1.0289200000000001</v>
@@ -1466,10 +1290,10 @@
       <c r="F18" s="10">
         <v>0.48469000000000001</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="20">
         <v>0.56686000000000003</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="10">
         <v>-1.14391</v>
       </c>
       <c r="I18" s="10">
@@ -1490,9 +1314,9 @@
       <c r="N18" s="6"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B19" s="10">
         <v>-0.99160999999999999</v>
@@ -1509,10 +1333,10 @@
       <c r="F19" s="10">
         <v>0.61629999999999996</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="20">
         <v>0.57511999999999996</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="10">
         <v>-1.10344</v>
       </c>
       <c r="I19" s="10">
@@ -1533,9 +1357,9 @@
       <c r="N19" s="6"/>
       <c r="O19" s="5"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B20" s="10">
         <v>-1.3285100000000001</v>
@@ -1552,10 +1376,10 @@
       <c r="F20" s="10">
         <v>0.31308999999999998</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="20">
         <v>0.39372000000000001</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="10">
         <v>-1.5029300000000001</v>
       </c>
       <c r="I20" s="10">
@@ -1576,9 +1400,9 @@
       <c r="N20" s="6"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B21" s="10">
         <v>-1.2311000000000001</v>
@@ -1595,10 +1419,10 @@
       <c r="F21" s="10">
         <v>0.39366000000000001</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="20">
         <v>0.10319</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="10">
         <v>-1.20326</v>
       </c>
       <c r="I21" s="10">
@@ -1619,9 +1443,9 @@
       <c r="N21" s="6"/>
       <c r="O21" s="5"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10">
         <v>-1.2001299999999999</v>
@@ -1638,10 +1462,10 @@
       <c r="F22" s="10">
         <v>0.54481000000000002</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="20">
         <v>0.40538000000000002</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="10">
         <v>-1.5470699999999999</v>
       </c>
       <c r="I22" s="10">
@@ -1662,9 +1486,9 @@
       <c r="N22" s="6"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B23" s="10">
         <v>-0.64963000000000004</v>
@@ -1681,10 +1505,10 @@
       <c r="F23" s="10">
         <v>0.69515000000000005</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="20">
         <v>0.90417999999999998</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="10">
         <v>-0.91156000000000004</v>
       </c>
       <c r="I23" s="10">
@@ -1705,9 +1529,9 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B24" s="14">
         <v>-1.2384500000000001</v>
@@ -1724,10 +1548,10 @@
       <c r="F24" s="14">
         <v>0.40405000000000002</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="21">
         <v>0.34589999999999999</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="14">
         <v>-1.19059</v>
       </c>
       <c r="I24" s="14">
@@ -1748,9 +1572,9 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B25" s="14">
         <v>-1.11273</v>
@@ -1767,10 +1591,10 @@
       <c r="F25" s="14">
         <v>0.59150000000000003</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="21">
         <v>0.51978000000000002</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="14">
         <v>-1.1856199999999999</v>
       </c>
       <c r="I25" s="14">
@@ -1791,9 +1615,9 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B26" s="7">
         <v>-0.39208999999999999</v>
@@ -1810,10 +1634,10 @@
       <c r="F26" s="7">
         <v>0.54696</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="18">
         <v>0.35596</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="7">
         <v>-0.75932999999999995</v>
       </c>
       <c r="I26" s="7">
@@ -1832,11 +1656,11 @@
         <v>-0.13963</v>
       </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="33"/>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="O26" s="26"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B27" s="7">
         <v>-0.56896000000000002</v>
@@ -1853,10 +1677,10 @@
       <c r="F27" s="7">
         <v>0.79117999999999999</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="18">
         <v>0.50422</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="7">
         <v>-0.96223999999999998</v>
       </c>
       <c r="I27" s="7">
@@ -1875,11 +1699,11 @@
         <v>-0.14398</v>
       </c>
       <c r="N27" s="6"/>
-      <c r="O27" s="33"/>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="O27" s="26"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B28" s="7">
         <v>-0.42202000000000001</v>
@@ -1896,10 +1720,10 @@
       <c r="F28" s="7">
         <v>0.29108000000000001</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="18">
         <v>0.57613999999999999</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="7">
         <v>-0.81196999999999997</v>
       </c>
       <c r="I28" s="7">
@@ -1918,11 +1742,11 @@
         <v>-0.10221</v>
       </c>
       <c r="N28" s="6"/>
-      <c r="O28" s="33"/>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="O28" s="26"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B29" s="7">
         <v>-0.70767000000000002</v>
@@ -1939,10 +1763,10 @@
       <c r="F29" s="7">
         <v>0.75675000000000003</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="18">
         <v>0.77195000000000003</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="7">
         <v>-1.02206</v>
       </c>
       <c r="I29" s="7">
@@ -1961,11 +1785,11 @@
         <v>-7.9149999999999998E-2</v>
       </c>
       <c r="N29" s="6"/>
-      <c r="O29" s="33"/>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="O29" s="26"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B30" s="7">
         <v>-0.66603999999999997</v>
@@ -1982,10 +1806,10 @@
       <c r="F30" s="7">
         <v>0.47387000000000001</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="18">
         <v>0.42149999999999999</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="7">
         <v>-0.97909000000000002</v>
       </c>
       <c r="I30" s="7">
@@ -2004,11 +1828,11 @@
         <v>5.9997900000000005E-4</v>
       </c>
       <c r="N30" s="6"/>
-      <c r="O30" s="33"/>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="O30" s="26"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B31" s="7">
         <v>-0.48704999999999998</v>
@@ -2025,10 +1849,10 @@
       <c r="F31" s="7">
         <v>0.90698000000000001</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="18">
         <v>0.96186000000000005</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="7">
         <v>-0.99087999999999998</v>
       </c>
       <c r="I31" s="7">
@@ -2047,11 +1871,11 @@
         <v>-6.8440000000000001E-2</v>
       </c>
       <c r="N31" s="6"/>
-      <c r="O31" s="33"/>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="O31" s="26"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B32" s="7">
         <v>-2.9870000000000001E-2</v>
@@ -2068,10 +1892,10 @@
       <c r="F32" s="7">
         <v>0.99134</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="18">
         <v>1.0642499999999999</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="7">
         <v>-0.70130999999999999</v>
       </c>
       <c r="I32" s="7">
@@ -2090,11 +1914,11 @@
         <v>-0.15862999999999999</v>
       </c>
       <c r="N32" s="6"/>
-      <c r="O32" s="33"/>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="O32" s="26"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B33" s="7">
         <v>-0.29933999999999999</v>
@@ -2111,10 +1935,10 @@
       <c r="F33" s="7">
         <v>0.96533000000000002</v>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="18">
         <v>0.74407999999999996</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="7">
         <v>-0.96665000000000001</v>
       </c>
       <c r="I33" s="7">
@@ -2133,11 +1957,11 @@
         <v>-8.1949999999999995E-2</v>
       </c>
       <c r="N33" s="6"/>
-      <c r="O33" s="33"/>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="O33" s="26"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B34" s="7">
         <v>-0.61001000000000005</v>
@@ -2154,10 +1978,10 @@
       <c r="F34" s="7">
         <v>0.92044999999999999</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="18">
         <v>1.0392300000000001</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="7">
         <v>-1.03199</v>
       </c>
       <c r="I34" s="7">
@@ -2176,11 +2000,11 @@
         <v>-0.10718999999999999</v>
       </c>
       <c r="N34" s="6"/>
-      <c r="O34" s="33"/>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="O34" s="26"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B35" s="7">
         <v>-5.7520000000000002E-2</v>
@@ -2197,10 +2021,10 @@
       <c r="F35" s="7">
         <v>0.52153000000000005</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="18">
         <v>1.2176800000000001</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="7">
         <v>-0.73714999999999997</v>
       </c>
       <c r="I35" s="7">
@@ -2219,11 +2043,11 @@
         <v>-6.4350000000000004E-2</v>
       </c>
       <c r="N35" s="6"/>
-      <c r="O35" s="33"/>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="O35" s="26"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B36" s="8">
         <v>-0.66220000000000001</v>
@@ -2240,10 +2064,10 @@
       <c r="F36" s="8">
         <v>0.65561999999999998</v>
       </c>
-      <c r="G36" s="28">
+      <c r="G36" s="22">
         <v>0.78100999999999998</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="8">
         <v>-1.0898399999999999</v>
       </c>
       <c r="I36" s="8">
@@ -2261,12 +2085,12 @@
       <c r="M36" s="8">
         <v>-0.13059999999999999</v>
       </c>
-      <c r="N36" s="31"/>
-      <c r="O36" s="33"/>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" s="25"/>
+      <c r="O36" s="26"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B37" s="8">
         <v>-0.78098000000000001</v>
@@ -2283,10 +2107,10 @@
       <c r="F37" s="8">
         <v>0.85670000000000002</v>
       </c>
-      <c r="G37" s="28">
+      <c r="G37" s="22">
         <v>0.88829000000000002</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="8">
         <v>-1.2143699999999999</v>
       </c>
       <c r="I37" s="8">
@@ -2304,12 +2128,12 @@
       <c r="M37" s="8">
         <v>-5.1889999999999999E-2</v>
       </c>
-      <c r="N37" s="31"/>
-      <c r="O37" s="33"/>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" s="25"/>
+      <c r="O37" s="26"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B38" s="8">
         <v>-0.55376000000000003</v>
@@ -2326,10 +2150,10 @@
       <c r="F38" s="8">
         <v>0.83738000000000001</v>
       </c>
-      <c r="G38" s="28">
+      <c r="G38" s="22">
         <v>0.80291000000000001</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="8">
         <v>-1.0318099999999999</v>
       </c>
       <c r="I38" s="8">
@@ -2347,12 +2171,12 @@
       <c r="M38" s="8">
         <v>-0.13119</v>
       </c>
-      <c r="N38" s="31"/>
-      <c r="O38" s="33"/>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" s="25"/>
+      <c r="O38" s="26"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B39" s="8">
         <v>-0.89495000000000002</v>
@@ -2369,10 +2193,10 @@
       <c r="F39" s="8">
         <v>0.81391999999999998</v>
       </c>
-      <c r="G39" s="28">
+      <c r="G39" s="22">
         <v>0.90324000000000004</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="8">
         <v>-1.0755600000000001</v>
       </c>
       <c r="I39" s="8">
@@ -2391,11 +2215,11 @@
         <v>-0.17080999999999999</v>
       </c>
       <c r="N39" s="6"/>
-      <c r="O39" s="33"/>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="O39" s="26"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B40" s="8">
         <v>-0.71077000000000001</v>
@@ -2412,10 +2236,10 @@
       <c r="F40" s="8">
         <v>0.79610999999999998</v>
       </c>
-      <c r="G40" s="28">
+      <c r="G40" s="22">
         <v>1.02826</v>
       </c>
-      <c r="H40" s="21">
+      <c r="H40" s="8">
         <v>-1.0949899999999999</v>
       </c>
       <c r="I40" s="8">
@@ -2434,11 +2258,11 @@
         <v>-0.11452</v>
       </c>
       <c r="N40" s="6"/>
-      <c r="O40" s="33"/>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="O40" s="26"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B41" s="9">
         <v>-0.31590000000000001</v>
@@ -2455,10 +2279,10 @@
       <c r="F41" s="9">
         <v>0.22073000000000001</v>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="23">
         <v>0.49919000000000002</v>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="9">
         <v>-1.4916799999999999</v>
       </c>
       <c r="I41" s="9">
@@ -2477,11 +2301,11 @@
         <v>0.23538999999999999</v>
       </c>
       <c r="N41" s="6"/>
-      <c r="O41" s="33"/>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="O41" s="26"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B42" s="9">
         <v>-0.33001000000000003</v>
@@ -2498,10 +2322,10 @@
       <c r="F42" s="9">
         <v>9.7259999999999999E-2</v>
       </c>
-      <c r="G42" s="29">
+      <c r="G42" s="23">
         <v>0.52871999999999997</v>
       </c>
-      <c r="H42" s="22">
+      <c r="H42" s="9">
         <v>-1.4953700000000001</v>
       </c>
       <c r="I42" s="9">
@@ -2520,11 +2344,11 @@
         <v>0.11815000000000001</v>
       </c>
       <c r="N42" s="6"/>
-      <c r="O42" s="33"/>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="O42" s="26"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B43" s="9">
         <v>-6.2469999999999998E-2</v>
@@ -2541,10 +2365,10 @@
       <c r="F43" s="9">
         <v>3.0190000000000002E-2</v>
       </c>
-      <c r="G43" s="29">
+      <c r="G43" s="23">
         <v>0.26845999999999998</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43" s="9">
         <v>-1.23054</v>
       </c>
       <c r="I43" s="9">
@@ -2563,11 +2387,11 @@
         <v>0.16491</v>
       </c>
       <c r="N43" s="6"/>
-      <c r="O43" s="33"/>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="O43" s="26"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B44" s="9">
         <v>-0.13936000000000001</v>
@@ -2584,10 +2408,10 @@
       <c r="F44" s="9">
         <v>0.24462999999999999</v>
       </c>
-      <c r="G44" s="29">
+      <c r="G44" s="23">
         <v>0.84353999999999996</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H44" s="9">
         <v>-1.57829</v>
       </c>
       <c r="I44" s="9">
@@ -2606,11 +2430,11 @@
         <v>0.11486</v>
       </c>
       <c r="N44" s="6"/>
-      <c r="O44" s="33"/>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="O44" s="26"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B45" s="9">
         <v>-0.18376000000000001</v>
@@ -2627,10 +2451,10 @@
       <c r="F45" s="9">
         <v>0.10345</v>
       </c>
-      <c r="G45" s="29">
+      <c r="G45" s="23">
         <v>0.41377999999999998</v>
       </c>
-      <c r="H45" s="22">
+      <c r="H45" s="9">
         <v>-1.2139599999999999</v>
       </c>
       <c r="I45" s="9">
@@ -2649,11 +2473,11 @@
         <v>0.29263</v>
       </c>
       <c r="N45" s="6"/>
-      <c r="O45" s="33"/>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="O45" s="26"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B46" s="9">
         <v>-1.7727200000000001</v>
@@ -2670,10 +2494,10 @@
       <c r="F46" s="9">
         <v>0.19416</v>
       </c>
-      <c r="G46" s="29">
+      <c r="G46" s="23">
         <v>0.33241999999999999</v>
       </c>
-      <c r="H46" s="22">
+      <c r="H46" s="9">
         <v>-1.56779</v>
       </c>
       <c r="I46" s="9">
@@ -2692,11 +2516,11 @@
         <v>0.18248</v>
       </c>
       <c r="N46" s="6"/>
-      <c r="O46" s="33"/>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="O46" s="26"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B47" s="9">
         <v>-0.47560999999999998</v>
@@ -2713,10 +2537,10 @@
       <c r="F47" s="9">
         <v>0.17455000000000001</v>
       </c>
-      <c r="G47" s="29">
+      <c r="G47" s="23">
         <v>0.40203</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="9">
         <v>-0.8034</v>
       </c>
       <c r="I47" s="9">
@@ -2735,11 +2559,11 @@
         <v>0.15412999999999999</v>
       </c>
       <c r="N47" s="6"/>
-      <c r="O47" s="33"/>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="O47" s="26"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B48" s="9">
         <v>-2.0097399999999999</v>
@@ -2756,10 +2580,10 @@
       <c r="F48" s="9">
         <v>0.34595999999999999</v>
       </c>
-      <c r="G48" s="29">
+      <c r="G48" s="23">
         <v>0.18651000000000001</v>
       </c>
-      <c r="H48" s="22">
+      <c r="H48" s="9">
         <v>-1.4373199999999999</v>
       </c>
       <c r="I48" s="9">
@@ -2778,11 +2602,11 @@
         <v>0.13389000000000001</v>
       </c>
       <c r="N48" s="6"/>
-      <c r="O48" s="33"/>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="O48" s="26"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B49" s="9">
         <v>-1.6427700000000001</v>
@@ -2799,10 +2623,10 @@
       <c r="F49" s="9">
         <v>0.24956999999999999</v>
       </c>
-      <c r="G49" s="29">
+      <c r="G49" s="23">
         <v>0.32388</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="9">
         <v>-1.23627</v>
       </c>
       <c r="I49" s="9">
@@ -2821,11 +2645,11 @@
         <v>0.12216</v>
       </c>
       <c r="N49" s="6"/>
-      <c r="O49" s="33"/>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="O49" s="26"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B50" s="9">
         <v>-0.39573000000000003</v>
@@ -2842,10 +2666,10 @@
       <c r="F50" s="9">
         <v>0.11547</v>
       </c>
-      <c r="G50" s="29">
+      <c r="G50" s="23">
         <v>0.51712999999999998</v>
       </c>
-      <c r="H50" s="22">
+      <c r="H50" s="9">
         <v>-0.81430000000000002</v>
       </c>
       <c r="I50" s="9">
@@ -2864,11 +2688,11 @@
         <v>0.23665</v>
       </c>
       <c r="N50" s="6"/>
-      <c r="O50" s="33"/>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="O50" s="26"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B51" s="10">
         <v>-1.1490400000000001</v>
@@ -2885,10 +2709,10 @@
       <c r="F51" s="10">
         <v>0.46581</v>
       </c>
-      <c r="G51" s="26">
+      <c r="G51" s="20">
         <v>0.46703</v>
       </c>
-      <c r="H51" s="19">
+      <c r="H51" s="10">
         <v>-1.02166</v>
       </c>
       <c r="I51" s="10">
@@ -2907,11 +2731,11 @@
         <v>0.14882000000000001</v>
       </c>
       <c r="N51" s="6"/>
-      <c r="O51" s="35"/>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="O51" s="27"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B52" s="10">
         <v>-1.0389600000000001</v>
@@ -2928,10 +2752,10 @@
       <c r="F52" s="10">
         <v>0.53713</v>
       </c>
-      <c r="G52" s="26">
+      <c r="G52" s="20">
         <v>0.54213999999999996</v>
       </c>
-      <c r="H52" s="19">
+      <c r="H52" s="10">
         <v>-1.18241</v>
       </c>
       <c r="I52" s="10">
@@ -2950,11 +2774,11 @@
         <v>0.11720999999999999</v>
       </c>
       <c r="N52" s="6"/>
-      <c r="O52" s="35"/>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="O52" s="27"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B53" s="10">
         <v>-1.0233099999999999</v>
@@ -2971,10 +2795,10 @@
       <c r="F53" s="10">
         <v>0.40153</v>
       </c>
-      <c r="G53" s="26">
+      <c r="G53" s="20">
         <v>0.64505000000000001</v>
       </c>
-      <c r="H53" s="19">
+      <c r="H53" s="10">
         <v>-1.0844499999999999</v>
       </c>
       <c r="I53" s="10">
@@ -2993,11 +2817,11 @@
         <v>6.9360000000000005E-2</v>
       </c>
       <c r="N53" s="6"/>
-      <c r="O53" s="35"/>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="O53" s="27"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B54" s="10">
         <v>-1.02613</v>
@@ -3014,10 +2838,10 @@
       <c r="F54" s="10">
         <v>0.37025000000000002</v>
       </c>
-      <c r="G54" s="26">
+      <c r="G54" s="20">
         <v>0.69282999999999995</v>
       </c>
-      <c r="H54" s="19">
+      <c r="H54" s="10">
         <v>-1.2099800000000001</v>
       </c>
       <c r="I54" s="10">
@@ -3036,11 +2860,11 @@
         <v>9.0740000000000001E-2</v>
       </c>
       <c r="N54" s="6"/>
-      <c r="O54" s="35"/>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="O54" s="27"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B55" s="10">
         <v>-1.0631999999999999</v>
@@ -3057,10 +2881,10 @@
       <c r="F55" s="10">
         <v>0.58337000000000006</v>
       </c>
-      <c r="G55" s="26">
+      <c r="G55" s="20">
         <v>0.73767000000000005</v>
       </c>
-      <c r="H55" s="19">
+      <c r="H55" s="10">
         <v>-1.0321</v>
       </c>
       <c r="I55" s="10">
@@ -3079,11 +2903,11 @@
         <v>3.6670000000000001E-2</v>
       </c>
       <c r="N55" s="6"/>
-      <c r="O55" s="35"/>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="O55" s="27"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B56" s="10">
         <v>-0.92886999999999997</v>
@@ -3100,10 +2924,10 @@
       <c r="F56" s="10">
         <v>0.40726000000000001</v>
       </c>
-      <c r="G56" s="26">
+      <c r="G56" s="20">
         <v>0.82381000000000004</v>
       </c>
-      <c r="H56" s="19">
+      <c r="H56" s="10">
         <v>-0.86194000000000004</v>
       </c>
       <c r="I56" s="10">
@@ -3122,11 +2946,11 @@
         <v>0.11298</v>
       </c>
       <c r="N56" s="6"/>
-      <c r="O56" s="35"/>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="O56" s="27"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B57" s="10">
         <v>-1.2353099999999999</v>
@@ -3143,10 +2967,10 @@
       <c r="F57" s="10">
         <v>0.42758000000000002</v>
       </c>
-      <c r="G57" s="26">
+      <c r="G57" s="20">
         <v>0.65578000000000003</v>
       </c>
-      <c r="H57" s="19">
+      <c r="H57" s="10">
         <v>-1.01468</v>
       </c>
       <c r="I57" s="10">
@@ -3165,11 +2989,11 @@
         <v>9.0660000000000004E-2</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="35"/>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="O57" s="27"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B58" s="10">
         <v>-0.94255</v>
@@ -3186,10 +3010,10 @@
       <c r="F58" s="10">
         <v>0.47559000000000001</v>
       </c>
-      <c r="G58" s="26">
+      <c r="G58" s="20">
         <v>0.72291000000000005</v>
       </c>
-      <c r="H58" s="19">
+      <c r="H58" s="10">
         <v>-0.83350999999999997</v>
       </c>
       <c r="I58" s="10">
@@ -3208,11 +3032,11 @@
         <v>9.8089999999999997E-2</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="35"/>
-    </row>
-    <row r="59" spans="1:15" s="1" customFormat="1">
+      <c r="O58" s="27"/>
+    </row>
+    <row r="59" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B59" s="15">
         <v>-1.75095</v>
@@ -3251,11 +3075,11 @@
         <v>6.0940000000000001E-2</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="33"/>
-    </row>
-    <row r="60" spans="1:15" s="1" customFormat="1">
+      <c r="O59" s="26"/>
+    </row>
+    <row r="60" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B60" s="15">
         <v>-1.6730100000000001</v>
@@ -3294,11 +3118,11 @@
         <v>-0.21676999999999999</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="33"/>
-    </row>
-    <row r="61" spans="1:15" s="1" customFormat="1">
+      <c r="O60" s="26"/>
+    </row>
+    <row r="61" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B61" s="15">
         <v>-1.7214100000000001</v>
@@ -3337,11 +3161,11 @@
         <v>-0.23601</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="33"/>
-    </row>
-    <row r="62" spans="1:15" s="1" customFormat="1">
+      <c r="O61" s="26"/>
+    </row>
+    <row r="62" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B62" s="15">
         <v>-1.4542999999999999</v>
@@ -3380,11 +3204,11 @@
         <v>-0.10534</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="33"/>
-    </row>
-    <row r="63" spans="1:15" s="1" customFormat="1">
+      <c r="O62" s="26"/>
+    </row>
+    <row r="63" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B63" s="15">
         <v>-1.41262</v>
@@ -3423,9 +3247,9 @@
         <v>-0.10077</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="33"/>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="O63" s="26"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O64" s="2"/>
     </row>
   </sheetData>
@@ -3433,416 +3257,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F71ABEF9-A70A-4BCD-BD00-D07D1A5FD3F1}">
-  <dimension ref="A1:G64"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="5"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="32"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="32"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="32"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="32"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="32"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="32"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="32"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="32"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="32"/>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" s="32"/>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="32"/>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="32"/>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="32"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="32"/>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" s="32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="32"/>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="32"/>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="32"/>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" s="32"/>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" s="32"/>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="32"/>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" s="32"/>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="32"/>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="32"/>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="34"/>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" s="34"/>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="34"/>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" s="34"/>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B56" s="34"/>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="34"/>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="34"/>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="32"/>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B61" s="32"/>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B62" s="32"/>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" s="32"/>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="B64" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B26:B40"/>
-    <mergeCell ref="B41:B50"/>
-    <mergeCell ref="B51:B58"/>
-    <mergeCell ref="B59:B63"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Early cancer detection/TS Train.xlsx
+++ b/Early cancer detection/TS Train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSoft\Pycharm\PythonProject\PythonProject\Archive\01_tri_cancer_screening\Source code for submission\Early cancer detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B06914B-BF4C-423A-A193-9CE9487A09E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C4550B-AB1A-4E24-8241-6E3E8351A881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,83 +112,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -197,61 +149,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -530,1738 +452,1756 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6E636D38-821F-41D9-A09D-5C62AB7C5517}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;0c85d0ae-1aee-4213-acfa-6780bb583839&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4D32A6-BAC1-4CF0-87E7-2BD375B36B4D}">
   <dimension ref="A1:O64"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="1" customWidth="1"/>
-    <col min="2" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="8.88671875" style="24"/>
-    <col min="8" max="13" width="8.88671875" style="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="3" customWidth="1"/>
+    <col min="2" max="13" width="8.88671875" style="3"/>
+    <col min="14" max="14" width="25" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="9">
         <v>-1.04538</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="9">
         <v>-5.8349999999999999E-2</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="9">
         <v>-0.81257000000000001</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="9">
         <v>-1.69994</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="9">
         <v>0.83172000000000001</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="9">
         <v>0.29249999999999998</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="9">
         <v>-0.61443000000000003</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="9">
         <v>-1.7766500000000001</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="9">
         <v>0.23738000000000001</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="9">
         <v>2.36707</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="9">
         <v>-6.6180000000000003E-2</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="9">
         <v>-8.9200000000000002E-2</v>
       </c>
-      <c r="N2" s="6"/>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:15">
+      <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="9">
         <v>-0.70243</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="9">
         <v>0.62751000000000001</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="9">
         <v>-0.44296000000000002</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="9">
         <v>-1.4558599999999999</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="9">
         <v>0.54937999999999998</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="9">
         <v>0.58689000000000002</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="9">
         <v>-0.40277000000000002</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="9">
         <v>-1.7512399999999999</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="9">
         <v>0.41675000000000001</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="9">
         <v>2.1371600000000002</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="9">
         <v>-3.9570000000000001E-2</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="9">
         <v>1.35E-2</v>
       </c>
-      <c r="N3" s="6"/>
+      <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:15">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <v>-1.30525</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="9">
         <v>0.22944000000000001</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <v>-0.83274000000000004</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <v>-2.0259499999999999</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="9">
         <v>0.22789000000000001</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="9">
         <v>-3.397E-2</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <v>-0.67196999999999996</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="9">
         <v>-1.81033</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="9">
         <v>0.43114000000000002</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="9">
         <v>2.3549899999999999</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="9">
         <v>1.9869999999999999E-2</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="9">
         <v>-0.11183999999999999</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="N4" s="2"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>-0.63944999999999996</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>1.1156999999999999</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>-0.37375999999999998</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>-1.1480600000000001</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>0.26618000000000003</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="9">
         <v>0.67571000000000003</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>-0.52639999999999998</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>-1.99559</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>0.27921000000000001</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>1.9729099999999999</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="9">
         <v>6.9550000000000001E-2</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="9">
         <v>-5.91E-2</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="N5" s="2"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>-1.1816199999999999</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <v>-0.37408999999999998</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <v>-0.35843999999999998</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>-1.5754900000000001</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>-0.63887000000000005</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="9">
         <v>-0.20804</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <v>-1.5779999999999999E-2</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <v>-2.1646100000000001</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <v>0.34181</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="9">
         <v>2.02658</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="9">
         <v>-0.12214</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="9">
         <v>-3.5899999999999999E-3</v>
       </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>-0.87936000000000003</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="9">
         <v>-9.8280000000000006E-2</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <v>-0.46217000000000003</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>-1.9972399999999999</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>0.20882999999999999</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="9">
         <v>0.58726999999999996</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <v>-0.49909999999999999</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="9">
         <v>-2.2115100000000001</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="9">
         <v>0.38231999999999999</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="9">
         <v>2.0796199999999998</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="9">
         <v>1.508E-2</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="9">
         <v>-8.6199999999999992E-3</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N7" s="2"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="8">
         <v>0.35000999999999999</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="8">
         <v>0.86870000000000003</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="8">
         <v>-1.2810999999999999</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="8">
         <v>-0.61</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="8">
         <v>2.5870000000000001E-2</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="8">
         <v>0.24604999999999999</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="8">
         <v>-0.89485999999999999</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="8">
         <v>0.58650999999999998</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="8">
         <v>0.49493999999999999</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="8">
         <v>2.3099799999999999</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="8">
         <v>-7.4800000000000005E-2</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="8">
         <v>-0.10015</v>
       </c>
-      <c r="N8" s="12"/>
+      <c r="N8" s="4"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="8">
         <v>-1.1359300000000001</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="8">
         <v>1.2631399999999999</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="8">
         <v>-1.06067</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="8">
         <v>-0.35343999999999998</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="8">
         <v>0.66785000000000005</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="8">
         <v>0.82333000000000001</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="8">
         <v>-1.10778</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="8">
         <v>0.28684999999999999</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="8">
         <v>0.76724999999999999</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="8">
         <v>0.96355999999999997</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="8">
         <v>-0.58364000000000005</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="8">
         <v>-0.26879999999999998</v>
       </c>
-      <c r="N9" s="12"/>
+      <c r="N9" s="4"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="8">
         <v>-1.13063</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="8">
         <v>1.3046800000000001</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="8">
         <v>-1.0992599999999999</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="8">
         <v>-0.22735</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="8">
         <v>0.59038000000000002</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="8">
         <v>0.58965999999999996</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="8">
         <v>-1.33385</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="8">
         <v>8.1700000000000002E-3</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="8">
         <v>0.74312</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="8">
         <v>1.4826900000000001</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="8">
         <v>-0.29959999999999998</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="8">
         <v>-0.21112</v>
       </c>
-      <c r="N10" s="12"/>
+      <c r="N10" s="4"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="8">
         <v>-1.4419</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="8">
         <v>-0.69091999999999998</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="8">
         <v>0.83977999999999997</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="8">
         <v>-2.1839400000000002</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="8">
         <v>-1.31118</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="8">
         <v>-1.04915</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="8">
         <v>-0.25669999999999998</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="8">
         <v>-0.26859</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="8">
         <v>0.94030999999999998</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="8">
         <v>2.28973</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="8">
         <v>-0.18303</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="8">
         <v>0.16705999999999999</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="4"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N11" s="4"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="8">
         <v>-1.4561299999999999</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="8">
         <v>0.64917999999999998</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="8">
         <v>-1.61114</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="8">
         <v>-1.2473700000000001</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="8">
         <v>0.56967999999999996</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="8">
         <v>0.34127000000000002</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="8">
         <v>-1.3644400000000001</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="8">
         <v>0.64188999999999996</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="8">
         <v>0.61197000000000001</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="8">
         <v>1.56335</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="8">
         <v>-0.26871</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="8">
         <v>-0.15612999999999999</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N12" s="4"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="8">
         <v>2.1588599999999998</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="8">
         <v>1.6730799999999999</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="8">
         <v>2.6048200000000001</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="8">
         <v>-1.0597399999999999</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="8">
         <v>-5.2220000000000003E-2</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="8">
         <v>-0.40466000000000002</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="8">
         <v>-0.48393000000000003</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="8">
         <v>-0.80922000000000005</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="8">
         <v>0.76890999999999998</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="8">
         <v>2.1620200000000001</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="8">
         <v>-0.27335999999999999</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="8">
         <v>-0.40461000000000003</v>
       </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N13" s="4"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="8">
         <v>1.2878499999999999</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="8">
         <v>2.4138299999999999</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="8">
         <v>2.3342000000000001</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="8">
         <v>-1.02528</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="8">
         <v>0.25631999999999999</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="8">
         <v>8.6800000000000002E-2</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="8">
         <v>-0.58352999999999999</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="8">
         <v>-1.02393</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="8">
         <v>0.77539000000000002</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="8">
         <v>1.63713</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="8">
         <v>-0.44938</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="8">
         <v>-0.48610999999999999</v>
       </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N14" s="4"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="8">
         <v>-0.56979999999999997</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="8">
         <v>2.4374899999999999</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="8">
         <v>0.94047999999999998</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="8">
         <v>-0.84433000000000002</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="8">
         <v>0.33300999999999997</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="8">
         <v>-0.21743999999999999</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="8">
         <v>-0.67100000000000004</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="8">
         <v>-0.97572000000000003</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="8">
         <v>0.97172999999999998</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="8">
         <v>1.62293</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="8">
         <v>-0.57991000000000004</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="8">
         <v>-0.27938000000000002</v>
       </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N15" s="4"/>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="8">
         <v>-1.2387900000000001</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="8">
         <v>0.56015000000000004</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="8">
         <v>1.0410000000000001E-2</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="8">
         <v>-0.61543999999999999</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="8">
         <v>0.21582999999999999</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="8">
         <v>-0.40648000000000001</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="8">
         <v>-1.4386699999999999</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="8">
         <v>-0.39615</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="8">
         <v>0.47893999999999998</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="8">
         <v>2.0533199999999998</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="8">
         <v>-0.36889</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="8">
         <v>-0.54744000000000004</v>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="4"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="N16" s="4"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>-0.87280999999999997</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>2.2119200000000001</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>-0.60909999999999997</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>-0.69018000000000002</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>0.65042999999999995</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="9">
         <v>0.70631999999999995</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <v>-1.1612</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>-0.64598</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <v>0.17612</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
         <v>1.8828</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>0.20391999999999999</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>6.5269999999999995E-2</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="4"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="N17" s="2"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>-1.0289200000000001</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>2.3278400000000001</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>-0.65620000000000001</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>-0.63734000000000002</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>0.48469000000000001</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="9">
         <v>0.56686000000000003</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <v>-1.14391</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>-0.71696000000000004</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <v>0.16553999999999999</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="9">
         <v>1.86547</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>1.389E-2</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <v>0.1802</v>
       </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="4"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="N18" s="2"/>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>-0.99160999999999999</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>1.7035499999999999</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>-0.80544000000000004</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>-0.77998000000000001</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>0.61629999999999996</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="9">
         <v>0.57511999999999996</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <v>-1.10344</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <v>-0.53969</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>0.16087000000000001</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="9">
         <v>1.57847</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>-5.3099999999999996E-3</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="9">
         <v>3.1230000000000001E-2</v>
       </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>-1.3285100000000001</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>1.58196</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>-0.75519000000000003</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>-0.63107000000000002</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>0.31308999999999998</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="9">
         <v>0.39372000000000001</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <v>-1.5029300000000001</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <v>-1.5607899999999999</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="9">
         <v>0.15187999999999999</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="9">
         <v>1.25125</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>-8.8160000000000002E-2</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="9">
         <v>-0.11311</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>-1.2311000000000001</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>1.15306</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>-0.90417000000000003</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>-1.14998</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>0.39366000000000001</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="9">
         <v>0.10319</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="9">
         <v>-1.20326</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <v>-0.92942000000000002</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="9">
         <v>0.31734000000000001</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="9">
         <v>2.4056000000000002</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>1.478E-2</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="9">
         <v>7.5939999999999994E-2</v>
       </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>-1.2001299999999999</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>1.11839</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>-1.03348</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>-1.11063</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="9">
         <v>0.54481000000000002</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="9">
         <v>0.40538000000000002</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="9">
         <v>-1.5470699999999999</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="9">
         <v>-1.23533</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="9">
         <v>0.15293000000000001</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="9">
         <v>2.1987199999999998</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="9">
         <v>-0.28239999999999998</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="9">
         <v>2.97E-3</v>
       </c>
-      <c r="N22" s="6"/>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>-0.64963000000000004</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>1.9219599999999999</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>-0.77237999999999996</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>-0.14152000000000001</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>0.69515000000000005</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="9">
         <v>0.90417999999999998</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="9">
         <v>-0.91156000000000004</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="9">
         <v>-1.5380499999999999</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="9">
         <v>6.7309999999999995E-2</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="9">
         <v>0.88119000000000003</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="9">
         <v>5.5140000000000002E-2</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="9">
         <v>2.6009999999999998E-2</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15">
       <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="9">
         <v>-1.2384500000000001</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="9">
         <v>0.78942000000000001</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="9">
         <v>-1.12053</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="9">
         <v>-1.05284</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="9">
         <v>0.40405000000000002</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="9">
         <v>0.34589999999999999</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="9">
         <v>-1.19059</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="9">
         <v>-1.51637</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="9">
         <v>2.375E-2</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="9">
         <v>1.5429999999999999</v>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="9">
         <v>-2.8469999999999999E-2</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M24" s="9">
         <v>3.4459999999999998E-2</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="9">
         <v>-1.11273</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="9">
         <v>1.1352100000000001</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="9">
         <v>-1.15838</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="9">
         <v>-1.03823</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="9">
         <v>0.59150000000000003</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="9">
         <v>0.51978000000000002</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="9">
         <v>-1.1856199999999999</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="9">
         <v>-0.63349</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="9">
         <v>5.1679999999999997E-2</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="9">
         <v>2.06169</v>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="9">
         <v>0.17624999999999999</v>
       </c>
-      <c r="M25" s="14">
+      <c r="M25" s="9">
         <v>-5.4850000000000003E-2</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="7">
+    <row r="26" spans="1:15">
+      <c r="A26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="9">
         <v>-0.39208999999999999</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="9">
         <v>1.9411499999999999</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="9">
         <v>-0.29826999999999998</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="9">
         <v>-0.75495000000000001</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="9">
         <v>0.54696</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="9">
         <v>0.35596</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="9">
         <v>-0.75932999999999995</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="9">
         <v>-0.56149000000000004</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="9">
         <v>0.23179</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="9">
         <v>1.68075</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="9">
         <v>1.7010000000000001E-2</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="9">
         <v>-0.13963</v>
       </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="26"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="7">
+      <c r="N26" s="2"/>
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="9">
         <v>-0.56896000000000002</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="9">
         <v>1.9326300000000001</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="9">
         <v>-0.60541999999999996</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="9">
         <v>-0.81647999999999998</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="9">
         <v>0.79117999999999999</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="9">
         <v>0.50422</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="9">
         <v>-0.96223999999999998</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="9">
         <v>-0.63665000000000005</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="9">
         <v>0.27095999999999998</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="9">
         <v>1.89764</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="9">
         <v>-4.1759999999999999E-2</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="9">
         <v>-0.14398</v>
       </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="26"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="7">
+      <c r="N27" s="2"/>
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="9">
         <v>-0.42202000000000001</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="9">
         <v>2.6092</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="9">
         <v>-0.23857999999999999</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="9">
         <v>-0.77546000000000004</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="9">
         <v>0.29108000000000001</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="9">
         <v>0.57613999999999999</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="9">
         <v>-0.81196999999999997</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="9">
         <v>-1.0340100000000001</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="9">
         <v>0.29370000000000002</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="9">
         <v>1.0287599999999999</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="9">
         <v>-4.7199999999999999E-2</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="9">
         <v>-0.10221</v>
       </c>
-      <c r="N28" s="6"/>
-      <c r="O28" s="26"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="7">
+      <c r="N28" s="2"/>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="9">
         <v>-0.70767000000000002</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="9">
         <v>2.4695200000000002</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="9">
         <v>-0.59891000000000005</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="9">
         <v>-0.52212000000000003</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="9">
         <v>0.75675000000000003</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="9">
         <v>0.77195000000000003</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="9">
         <v>-1.02206</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="9">
         <v>-0.96457999999999999</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="9">
         <v>0.21429000000000001</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="9">
         <v>1.39364</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L29" s="9">
         <v>-3.3820000000000003E-2</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="9">
         <v>-7.9149999999999998E-2</v>
       </c>
-      <c r="N29" s="6"/>
-      <c r="O29" s="26"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="7">
+      <c r="N29" s="2"/>
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="9">
         <v>-0.66603999999999997</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="9">
         <v>1.77485</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="9">
         <v>0.12747</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="9">
         <v>-0.73858999999999997</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="9">
         <v>0.47387000000000001</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="9">
         <v>0.42149999999999999</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="9">
         <v>-0.97909000000000002</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I30" s="9">
         <v>-0.45984999999999998</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="9">
         <v>0.30879000000000001</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="9">
         <v>1.1935199999999999</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L30" s="9">
         <v>3.15E-3</v>
       </c>
-      <c r="M30" s="11">
+      <c r="M30" s="9">
         <v>5.9997900000000005E-4</v>
       </c>
-      <c r="N30" s="6"/>
-      <c r="O30" s="26"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="7">
+      <c r="N30" s="2"/>
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="9">
         <v>-0.48704999999999998</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="9">
         <v>1.6738599999999999</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="9">
         <v>-0.42348000000000002</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="9">
         <v>-0.77519000000000005</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="9">
         <v>0.90698000000000001</v>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="9">
         <v>0.96186000000000005</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="9">
         <v>-0.99087999999999998</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I31" s="9">
         <v>-0.97604999999999997</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="9">
         <v>0.27794000000000002</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="9">
         <v>1.5330699999999999</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L31" s="9">
         <v>-2.4760000000000001E-2</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="9">
         <v>-6.8440000000000001E-2</v>
       </c>
-      <c r="N31" s="6"/>
-      <c r="O31" s="26"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="7">
+      <c r="N31" s="2"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="9">
         <v>-2.9870000000000001E-2</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="9">
         <v>2.90055</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="9">
         <v>-0.49697999999999998</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="9">
         <v>-0.69964000000000004</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="9">
         <v>0.99134</v>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="9">
         <v>1.0642499999999999</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="9">
         <v>-0.70130999999999999</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="9">
         <v>-1.5623100000000001</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="9">
         <v>0.33260000000000001</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="9">
         <v>1.8492200000000001</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L32" s="9">
         <v>7.4700000000000001E-3</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M32" s="9">
         <v>-0.15862999999999999</v>
       </c>
-      <c r="N32" s="6"/>
-      <c r="O32" s="26"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N32" s="2"/>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="9">
         <v>-0.29933999999999999</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="9">
         <v>1.6213599999999999</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="9">
         <v>-0.18296000000000001</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="9">
         <v>-0.4244</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="9">
         <v>0.96533000000000002</v>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="9">
         <v>0.74407999999999996</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="9">
         <v>-0.96665000000000001</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I33" s="9">
         <v>-0.70667000000000002</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J33" s="9">
         <v>0.2959</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="9">
         <v>1.119</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L33" s="9">
         <v>-1.076E-2</v>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="9">
         <v>-8.1949999999999995E-2</v>
       </c>
-      <c r="N33" s="6"/>
-      <c r="O33" s="26"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N33" s="2"/>
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="9">
         <v>-0.61001000000000005</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="9">
         <v>2.2186699999999999</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="9">
         <v>0.51944999999999997</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="9">
         <v>-0.70750000000000002</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="9">
         <v>0.92044999999999999</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="9">
         <v>1.0392300000000001</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="9">
         <v>-1.03199</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="9">
         <v>-0.68991000000000002</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="9">
         <v>0.36273</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="9">
         <v>1.1753199999999999</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="9">
         <v>-2.334E-2</v>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="9">
         <v>-0.10718999999999999</v>
       </c>
-      <c r="N34" s="6"/>
-      <c r="O34" s="26"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N34" s="2"/>
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="9">
         <v>-5.7520000000000002E-2</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="9">
         <v>2.5375000000000001</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="9">
         <v>0.35310999999999998</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="9">
         <v>-0.88427999999999995</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="9">
         <v>0.52153000000000005</v>
       </c>
-      <c r="G35" s="18">
+      <c r="G35" s="9">
         <v>1.2176800000000001</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="9">
         <v>-0.73714999999999997</v>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="9">
         <v>-1.0313600000000001</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="9">
         <v>0.37636999999999998</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="9">
         <v>1.30846</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="9">
         <v>5.6340000000000001E-2</v>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="9">
         <v>-6.4350000000000004E-2</v>
       </c>
-      <c r="N35" s="6"/>
-      <c r="O35" s="26"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N35" s="2"/>
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="9">
         <v>-0.66220000000000001</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="9">
         <v>1.6597900000000001</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="9">
         <v>0.31236999999999998</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="9">
         <v>-0.27152999999999999</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="9">
         <v>0.65561999999999998</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="9">
         <v>0.78100999999999998</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="9">
         <v>-1.0898399999999999</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="9">
         <v>-1.3875299999999999</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="9">
         <v>0.12245</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="9">
         <v>0.99875000000000003</v>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="9">
         <v>-0.15206</v>
       </c>
-      <c r="M36" s="8">
+      <c r="M36" s="9">
         <v>-0.13059999999999999</v>
       </c>
-      <c r="N36" s="25"/>
-      <c r="O36" s="26"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N36" s="2"/>
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="9">
         <v>-0.78098000000000001</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="9">
         <v>1.7802500000000001</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="9">
         <v>0.92503999999999997</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="9">
         <v>-0.17588999999999999</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="9">
         <v>0.85670000000000002</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="9">
         <v>0.88829000000000002</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="9">
         <v>-1.2143699999999999</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="9">
         <v>-1.14514</v>
       </c>
-      <c r="J37" s="8">
+      <c r="J37" s="9">
         <v>0.24909000000000001</v>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="9">
         <v>1.4329000000000001</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="9">
         <v>-7.7280000000000001E-2</v>
       </c>
-      <c r="M37" s="8">
+      <c r="M37" s="9">
         <v>-5.1889999999999999E-2</v>
       </c>
-      <c r="N37" s="25"/>
-      <c r="O37" s="26"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N37" s="2"/>
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="9">
         <v>-0.55376000000000003</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="9">
         <v>1.55755</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="9">
         <v>0.33178999999999997</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="9">
         <v>-0.37086000000000002</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="9">
         <v>0.83738000000000001</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="9">
         <v>0.80291000000000001</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="9">
         <v>-1.0318099999999999</v>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="9">
         <v>-1.06511</v>
       </c>
-      <c r="J38" s="8">
+      <c r="J38" s="9">
         <v>9.6269999999999994E-2</v>
       </c>
-      <c r="K38" s="8">
+      <c r="K38" s="9">
         <v>1.44051</v>
       </c>
-      <c r="L38" s="8">
+      <c r="L38" s="9">
         <v>-0.15844</v>
       </c>
-      <c r="M38" s="8">
+      <c r="M38" s="9">
         <v>-0.13119</v>
       </c>
-      <c r="N38" s="25"/>
-      <c r="O38" s="26"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="N38" s="2"/>
+      <c r="O38" s="5"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="9">
         <v>-0.89495000000000002</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="9">
         <v>2.4396300000000002</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="9">
         <v>0.22559000000000001</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="9">
         <v>-4.1619999999999997E-2</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="9">
         <v>0.81391999999999998</v>
       </c>
-      <c r="G39" s="22">
+      <c r="G39" s="9">
         <v>0.90324000000000004</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="9">
         <v>-1.0755600000000001</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="9">
         <v>-1.0726</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="9">
         <v>8.831E-2</v>
       </c>
-      <c r="K39" s="8">
+      <c r="K39" s="9">
         <v>1.30094</v>
       </c>
-      <c r="L39" s="8">
+      <c r="L39" s="9">
         <v>-0.24052000000000001</v>
       </c>
-      <c r="M39" s="8">
+      <c r="M39" s="9">
         <v>-0.17080999999999999</v>
       </c>
-      <c r="N39" s="6"/>
-      <c r="O39" s="26"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="8">
+      <c r="N39" s="2"/>
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="9">
         <v>-0.71077000000000001</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="9">
         <v>3.3084199999999999</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="9">
         <v>0.27801999999999999</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="9">
         <v>-0.13976</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="9">
         <v>0.79610999999999998</v>
       </c>
-      <c r="G40" s="22">
+      <c r="G40" s="9">
         <v>1.02826</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="9">
         <v>-1.0949899999999999</v>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="9">
         <v>-1.23969</v>
       </c>
-      <c r="J40" s="8">
+      <c r="J40" s="9">
         <v>0.21185999999999999</v>
       </c>
-      <c r="K40" s="8">
+      <c r="K40" s="9">
         <v>1.2914300000000001</v>
       </c>
-      <c r="L40" s="8">
+      <c r="L40" s="9">
         <v>-9.3840000000000007E-2</v>
       </c>
-      <c r="M40" s="8">
+      <c r="M40" s="9">
         <v>-0.11452</v>
       </c>
-      <c r="N40" s="6"/>
-      <c r="O40" s="26"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="N40" s="2"/>
+      <c r="O40" s="5"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B41" s="9">
@@ -2279,7 +2219,7 @@
       <c r="F41" s="9">
         <v>0.22073000000000001</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="9">
         <v>0.49919000000000002</v>
       </c>
       <c r="H41" s="9">
@@ -2300,11 +2240,11 @@
       <c r="M41" s="9">
         <v>0.23538999999999999</v>
       </c>
-      <c r="N41" s="6"/>
-      <c r="O41" s="26"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="N41" s="2"/>
+      <c r="O41" s="5"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B42" s="9">
@@ -2322,7 +2262,7 @@
       <c r="F42" s="9">
         <v>9.7259999999999999E-2</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="9">
         <v>0.52871999999999997</v>
       </c>
       <c r="H42" s="9">
@@ -2343,11 +2283,11 @@
       <c r="M42" s="9">
         <v>0.11815000000000001</v>
       </c>
-      <c r="N42" s="6"/>
-      <c r="O42" s="26"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="N42" s="2"/>
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B43" s="9">
@@ -2365,7 +2305,7 @@
       <c r="F43" s="9">
         <v>3.0190000000000002E-2</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="9">
         <v>0.26845999999999998</v>
       </c>
       <c r="H43" s="9">
@@ -2386,11 +2326,11 @@
       <c r="M43" s="9">
         <v>0.16491</v>
       </c>
-      <c r="N43" s="6"/>
-      <c r="O43" s="26"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="N43" s="2"/>
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B44" s="9">
@@ -2408,7 +2348,7 @@
       <c r="F44" s="9">
         <v>0.24462999999999999</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="9">
         <v>0.84353999999999996</v>
       </c>
       <c r="H44" s="9">
@@ -2429,11 +2369,11 @@
       <c r="M44" s="9">
         <v>0.11486</v>
       </c>
-      <c r="N44" s="6"/>
-      <c r="O44" s="26"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="N44" s="2"/>
+      <c r="O44" s="5"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B45" s="9">
@@ -2451,7 +2391,7 @@
       <c r="F45" s="9">
         <v>0.10345</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="9">
         <v>0.41377999999999998</v>
       </c>
       <c r="H45" s="9">
@@ -2472,11 +2412,11 @@
       <c r="M45" s="9">
         <v>0.29263</v>
       </c>
-      <c r="N45" s="6"/>
-      <c r="O45" s="26"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="N45" s="2"/>
+      <c r="O45" s="5"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B46" s="9">
@@ -2494,7 +2434,7 @@
       <c r="F46" s="9">
         <v>0.19416</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="9">
         <v>0.33241999999999999</v>
       </c>
       <c r="H46" s="9">
@@ -2515,10 +2455,10 @@
       <c r="M46" s="9">
         <v>0.18248</v>
       </c>
-      <c r="N46" s="6"/>
-      <c r="O46" s="26"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N46" s="2"/>
+      <c r="O46" s="5"/>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -2537,7 +2477,7 @@
       <c r="F47" s="9">
         <v>0.17455000000000001</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="9">
         <v>0.40203</v>
       </c>
       <c r="H47" s="9">
@@ -2558,10 +2498,10 @@
       <c r="M47" s="9">
         <v>0.15412999999999999</v>
       </c>
-      <c r="N47" s="6"/>
-      <c r="O47" s="26"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N47" s="2"/>
+      <c r="O47" s="5"/>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="2" t="s">
         <v>14</v>
       </c>
@@ -2580,7 +2520,7 @@
       <c r="F48" s="9">
         <v>0.34595999999999999</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="9">
         <v>0.18651000000000001</v>
       </c>
       <c r="H48" s="9">
@@ -2601,10 +2541,10 @@
       <c r="M48" s="9">
         <v>0.13389000000000001</v>
       </c>
-      <c r="N48" s="6"/>
-      <c r="O48" s="26"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N48" s="2"/>
+      <c r="O48" s="5"/>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="2" t="s">
         <v>14</v>
       </c>
@@ -2623,7 +2563,7 @@
       <c r="F49" s="9">
         <v>0.24956999999999999</v>
       </c>
-      <c r="G49" s="23">
+      <c r="G49" s="9">
         <v>0.32388</v>
       </c>
       <c r="H49" s="9">
@@ -2644,10 +2584,10 @@
       <c r="M49" s="9">
         <v>0.12216</v>
       </c>
-      <c r="N49" s="6"/>
-      <c r="O49" s="26"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N49" s="2"/>
+      <c r="O49" s="5"/>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="2" t="s">
         <v>14</v>
       </c>
@@ -2666,7 +2606,7 @@
       <c r="F50" s="9">
         <v>0.11547</v>
       </c>
-      <c r="G50" s="23">
+      <c r="G50" s="9">
         <v>0.51712999999999998</v>
       </c>
       <c r="H50" s="9">
@@ -2687,569 +2627,569 @@
       <c r="M50" s="9">
         <v>0.23665</v>
       </c>
-      <c r="N50" s="6"/>
-      <c r="O50" s="26"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" s="10">
+      <c r="N50" s="2"/>
+      <c r="O50" s="5"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="9">
         <v>-1.1490400000000001</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="9">
         <v>2.0176799999999999</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="9">
         <v>-0.51153999999999999</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E51" s="9">
         <v>-0.65747999999999995</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="9">
         <v>0.46581</v>
       </c>
-      <c r="G51" s="20">
+      <c r="G51" s="9">
         <v>0.46703</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="9">
         <v>-1.02166</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I51" s="9">
         <v>-0.55003000000000002</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J51" s="9">
         <v>0.10706</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="9">
         <v>1.6839999999999999</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51" s="9">
         <v>4.8320000000000002E-2</v>
       </c>
-      <c r="M51" s="10">
+      <c r="M51" s="9">
         <v>0.14882000000000001</v>
       </c>
-      <c r="N51" s="6"/>
-      <c r="O51" s="27"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" s="10">
+      <c r="N51" s="2"/>
+      <c r="O51" s="6"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="9">
         <v>-1.0389600000000001</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="9">
         <v>1.5467200000000001</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="9">
         <v>-0.74046000000000001</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="9">
         <v>-0.85377999999999998</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="9">
         <v>0.53713</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="9">
         <v>0.54213999999999996</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="9">
         <v>-1.18241</v>
       </c>
-      <c r="I52" s="10">
+      <c r="I52" s="9">
         <v>-0.77405000000000002</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J52" s="9">
         <v>0.13070999999999999</v>
       </c>
-      <c r="K52" s="10">
+      <c r="K52" s="9">
         <v>2.0320399999999998</v>
       </c>
-      <c r="L52" s="10">
+      <c r="L52" s="9">
         <v>2.9260000000000001E-2</v>
       </c>
-      <c r="M52" s="10">
+      <c r="M52" s="9">
         <v>0.11720999999999999</v>
       </c>
-      <c r="N52" s="6"/>
-      <c r="O52" s="27"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="10">
+      <c r="N52" s="2"/>
+      <c r="O52" s="6"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="9">
         <v>-1.0233099999999999</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="9">
         <v>1.67971</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="9">
         <v>-0.50368000000000002</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="9">
         <v>-0.91849000000000003</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="9">
         <v>0.40153</v>
       </c>
-      <c r="G53" s="20">
+      <c r="G53" s="9">
         <v>0.64505000000000001</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="9">
         <v>-1.0844499999999999</v>
       </c>
-      <c r="I53" s="10">
+      <c r="I53" s="9">
         <v>-0.66829000000000005</v>
       </c>
-      <c r="J53" s="10">
+      <c r="J53" s="9">
         <v>8.4900000000000003E-2</v>
       </c>
-      <c r="K53" s="10">
+      <c r="K53" s="9">
         <v>2.26715</v>
       </c>
-      <c r="L53" s="10">
+      <c r="L53" s="9">
         <v>2.6540000000000001E-2</v>
       </c>
-      <c r="M53" s="10">
+      <c r="M53" s="9">
         <v>6.9360000000000005E-2</v>
       </c>
-      <c r="N53" s="6"/>
-      <c r="O53" s="27"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N53" s="2"/>
+      <c r="O53" s="6"/>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <v>-1.02613</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="9">
         <v>1.8043800000000001</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="9">
         <v>-0.53581999999999996</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="9">
         <v>-0.91744000000000003</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="9">
         <v>0.37025000000000002</v>
       </c>
-      <c r="G54" s="20">
+      <c r="G54" s="9">
         <v>0.69282999999999995</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="9">
         <v>-1.2099800000000001</v>
       </c>
-      <c r="I54" s="10">
+      <c r="I54" s="9">
         <v>-0.47610000000000002</v>
       </c>
-      <c r="J54" s="10">
+      <c r="J54" s="9">
         <v>-2.6540000000000001E-2</v>
       </c>
-      <c r="K54" s="10">
+      <c r="K54" s="9">
         <v>2.66534</v>
       </c>
-      <c r="L54" s="10">
+      <c r="L54" s="9">
         <v>0.17024</v>
       </c>
-      <c r="M54" s="10">
+      <c r="M54" s="9">
         <v>9.0740000000000001E-2</v>
       </c>
-      <c r="N54" s="6"/>
-      <c r="O54" s="27"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N54" s="2"/>
+      <c r="O54" s="6"/>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <v>-1.0631999999999999</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="9">
         <v>1.42469</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D55" s="9">
         <v>-0.75</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="9">
         <v>-0.79783000000000004</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="9">
         <v>0.58337000000000006</v>
       </c>
-      <c r="G55" s="20">
+      <c r="G55" s="9">
         <v>0.73767000000000005</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="9">
         <v>-1.0321</v>
       </c>
-      <c r="I55" s="10">
+      <c r="I55" s="9">
         <v>-0.79259000000000002</v>
       </c>
-      <c r="J55" s="10">
+      <c r="J55" s="9">
         <v>4.4600000000000004E-3</v>
       </c>
-      <c r="K55" s="10">
+      <c r="K55" s="9">
         <v>1.74088</v>
       </c>
-      <c r="L55" s="10">
+      <c r="L55" s="9">
         <v>-1.8859999999999998E-2</v>
       </c>
-      <c r="M55" s="10">
+      <c r="M55" s="9">
         <v>3.6670000000000001E-2</v>
       </c>
-      <c r="N55" s="6"/>
-      <c r="O55" s="27"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N55" s="2"/>
+      <c r="O55" s="6"/>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <v>-0.92886999999999997</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="9">
         <v>1.9514100000000001</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="9">
         <v>-0.59075999999999995</v>
       </c>
-      <c r="E56" s="10">
+      <c r="E56" s="9">
         <v>-0.80286000000000002</v>
       </c>
-      <c r="F56" s="10">
+      <c r="F56" s="9">
         <v>0.40726000000000001</v>
       </c>
-      <c r="G56" s="20">
+      <c r="G56" s="9">
         <v>0.82381000000000004</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H56" s="9">
         <v>-0.86194000000000004</v>
       </c>
-      <c r="I56" s="10">
+      <c r="I56" s="9">
         <v>-0.86648000000000003</v>
       </c>
-      <c r="J56" s="10">
+      <c r="J56" s="9">
         <v>-2.2300000000000002E-3</v>
       </c>
-      <c r="K56" s="10">
+      <c r="K56" s="9">
         <v>1.8903300000000001</v>
       </c>
-      <c r="L56" s="10">
+      <c r="L56" s="9">
         <v>0.10433000000000001</v>
       </c>
-      <c r="M56" s="10">
+      <c r="M56" s="9">
         <v>0.11298</v>
       </c>
-      <c r="N56" s="6"/>
-      <c r="O56" s="27"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N56" s="2"/>
+      <c r="O56" s="6"/>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <v>-1.2353099999999999</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="9">
         <v>1.33721</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="9">
         <v>-0.80889</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="9">
         <v>-1.15143</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57" s="9">
         <v>0.42758000000000002</v>
       </c>
-      <c r="G57" s="20">
+      <c r="G57" s="9">
         <v>0.65578000000000003</v>
       </c>
-      <c r="H57" s="10">
+      <c r="H57" s="9">
         <v>-1.01468</v>
       </c>
-      <c r="I57" s="10">
+      <c r="I57" s="9">
         <v>-0.43680999999999998</v>
       </c>
-      <c r="J57" s="10">
+      <c r="J57" s="9">
         <v>0.14002000000000001</v>
       </c>
-      <c r="K57" s="10">
+      <c r="K57" s="9">
         <v>1.89595</v>
       </c>
-      <c r="L57" s="10">
+      <c r="L57" s="9">
         <v>0.23089000000000001</v>
       </c>
-      <c r="M57" s="10">
+      <c r="M57" s="9">
         <v>9.0660000000000004E-2</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="27"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O57" s="6"/>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <v>-0.94255</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="9">
         <v>1.97116</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="9">
         <v>-0.58508000000000004</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="9">
         <v>-1.0865800000000001</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="9">
         <v>0.47559000000000001</v>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="9">
         <v>0.72291000000000005</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="9">
         <v>-0.83350999999999997</v>
       </c>
-      <c r="I58" s="10">
+      <c r="I58" s="9">
         <v>-1.7947200000000001</v>
       </c>
-      <c r="J58" s="10">
+      <c r="J58" s="9">
         <v>5.8430000000000003E-2</v>
       </c>
-      <c r="K58" s="10">
+      <c r="K58" s="9">
         <v>2.2436199999999999</v>
       </c>
-      <c r="L58" s="10">
+      <c r="L58" s="9">
         <v>-2.5479999999999999E-2</v>
       </c>
-      <c r="M58" s="10">
+      <c r="M58" s="9">
         <v>9.8089999999999997E-2</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="27"/>
-    </row>
-    <row r="59" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O58" s="6"/>
+    </row>
+    <row r="59" spans="1:15" s="3" customFormat="1">
       <c r="A59" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B59" s="15">
+      <c r="B59" s="9">
         <v>-1.75095</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C59" s="9">
         <v>1.1295999999999999</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="9">
         <v>-0.31839000000000001</v>
       </c>
-      <c r="E59" s="15">
+      <c r="E59" s="9">
         <v>-0.63078999999999996</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="9">
         <v>0.41748000000000002</v>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="9">
         <v>0.16336999999999999</v>
       </c>
-      <c r="H59" s="15">
+      <c r="H59" s="9">
         <v>-1.67886</v>
       </c>
-      <c r="I59" s="15">
+      <c r="I59" s="9">
         <v>0.57042999999999999</v>
       </c>
-      <c r="J59" s="15">
+      <c r="J59" s="9">
         <v>-0.49434</v>
       </c>
-      <c r="K59" s="15">
+      <c r="K59" s="9">
         <v>1.2363599999999999</v>
       </c>
-      <c r="L59" s="15">
+      <c r="L59" s="9">
         <v>-1.549E-2</v>
       </c>
-      <c r="M59" s="15">
+      <c r="M59" s="9">
         <v>6.0940000000000001E-2</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="26"/>
-    </row>
-    <row r="60" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O59" s="5"/>
+    </row>
+    <row r="60" spans="1:15" s="3" customFormat="1">
       <c r="A60" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B60" s="15">
+      <c r="B60" s="9">
         <v>-1.6730100000000001</v>
       </c>
-      <c r="C60" s="15">
+      <c r="C60" s="9">
         <v>0.57625999999999999</v>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="9">
         <v>4.7919999999999997E-2</v>
       </c>
-      <c r="E60" s="15">
+      <c r="E60" s="9">
         <v>-1.3299799999999999</v>
       </c>
-      <c r="F60" s="15">
+      <c r="F60" s="9">
         <v>0.40705999999999998</v>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="9">
         <v>0.68952000000000002</v>
       </c>
-      <c r="H60" s="15">
+      <c r="H60" s="9">
         <v>-1.5515000000000001</v>
       </c>
-      <c r="I60" s="15">
+      <c r="I60" s="9">
         <v>0.44877</v>
       </c>
-      <c r="J60" s="15">
+      <c r="J60" s="9">
         <v>-0.75209999999999999</v>
       </c>
-      <c r="K60" s="15">
+      <c r="K60" s="9">
         <v>1.8655299999999999</v>
       </c>
-      <c r="L60" s="15">
+      <c r="L60" s="9">
         <v>-0.13814000000000001</v>
       </c>
-      <c r="M60" s="15">
+      <c r="M60" s="9">
         <v>-0.21676999999999999</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="26"/>
-    </row>
-    <row r="61" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O60" s="5"/>
+    </row>
+    <row r="61" spans="1:15" s="3" customFormat="1">
       <c r="A61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B61" s="15">
+      <c r="B61" s="9">
         <v>-1.7214100000000001</v>
       </c>
-      <c r="C61" s="15">
+      <c r="C61" s="9">
         <v>0.33563999999999999</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="9">
         <v>-0.24657999999999999</v>
       </c>
-      <c r="E61" s="15">
+      <c r="E61" s="9">
         <v>-1.5463800000000001</v>
       </c>
-      <c r="F61" s="15">
+      <c r="F61" s="9">
         <v>0.19458</v>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="9">
         <v>0.51897000000000004</v>
       </c>
-      <c r="H61" s="15">
+      <c r="H61" s="9">
         <v>-1.69547</v>
       </c>
-      <c r="I61" s="15">
+      <c r="I61" s="9">
         <v>0.57084999999999997</v>
       </c>
-      <c r="J61" s="15">
+      <c r="J61" s="9">
         <v>-0.76724000000000003</v>
       </c>
-      <c r="K61" s="15">
+      <c r="K61" s="9">
         <v>2.2573500000000002</v>
       </c>
-      <c r="L61" s="15">
+      <c r="L61" s="9">
         <v>-0.36758000000000002</v>
       </c>
-      <c r="M61" s="15">
+      <c r="M61" s="9">
         <v>-0.23601</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="26"/>
-    </row>
-    <row r="62" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O61" s="5"/>
+    </row>
+    <row r="62" spans="1:15" s="3" customFormat="1">
       <c r="A62" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62" s="9">
         <v>-1.4542999999999999</v>
       </c>
-      <c r="C62" s="15">
+      <c r="C62" s="9">
         <v>1.8724400000000001</v>
       </c>
-      <c r="D62" s="15">
+      <c r="D62" s="9">
         <v>0.65219000000000005</v>
       </c>
-      <c r="E62" s="15">
+      <c r="E62" s="9">
         <v>-0.77830999999999995</v>
       </c>
-      <c r="F62" s="15">
+      <c r="F62" s="9">
         <v>0.58396000000000003</v>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="9">
         <v>0.91164999999999996</v>
       </c>
-      <c r="H62" s="15">
+      <c r="H62" s="9">
         <v>-1.5523899999999999</v>
       </c>
-      <c r="I62" s="15">
+      <c r="I62" s="9">
         <v>0.36637999999999998</v>
       </c>
-      <c r="J62" s="15">
+      <c r="J62" s="9">
         <v>-0.39689000000000002</v>
       </c>
-      <c r="K62" s="15">
+      <c r="K62" s="9">
         <v>1.44339</v>
       </c>
-      <c r="L62" s="15">
+      <c r="L62" s="9">
         <v>-4.5850000000000002E-2</v>
       </c>
-      <c r="M62" s="15">
+      <c r="M62" s="9">
         <v>-0.10534</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="26"/>
-    </row>
-    <row r="63" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O62" s="5"/>
+    </row>
+    <row r="63" spans="1:15" s="3" customFormat="1">
       <c r="A63" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63" s="9">
         <v>-1.41262</v>
       </c>
-      <c r="C63" s="15">
+      <c r="C63" s="9">
         <v>1.13812</v>
       </c>
-      <c r="D63" s="15">
+      <c r="D63" s="9">
         <v>0.37431999999999999</v>
       </c>
-      <c r="E63" s="15">
+      <c r="E63" s="9">
         <v>-0.98475000000000001</v>
       </c>
-      <c r="F63" s="15">
+      <c r="F63" s="9">
         <v>0.46444000000000002</v>
       </c>
-      <c r="G63" s="16">
+      <c r="G63" s="9">
         <v>1.2065300000000001</v>
       </c>
-      <c r="H63" s="15">
+      <c r="H63" s="9">
         <v>-1.49885</v>
       </c>
-      <c r="I63" s="15">
+      <c r="I63" s="9">
         <v>0.55715000000000003</v>
       </c>
-      <c r="J63" s="15">
+      <c r="J63" s="9">
         <v>-0.64786999999999995</v>
       </c>
-      <c r="K63" s="15">
+      <c r="K63" s="9">
         <v>2.2547100000000002</v>
       </c>
-      <c r="L63" s="15">
+      <c r="L63" s="9">
         <v>-3.8859999999999999E-2</v>
       </c>
-      <c r="M63" s="15">
+      <c r="M63" s="9">
         <v>-0.10077</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="26"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O63" s="5"/>
+    </row>
+    <row r="64" spans="1:15">
       <c r="O64" s="2"/>
     </row>
   </sheetData>
